--- a/group_input/M3_Liq_2C_WPD_InersiaCap_RevLoad.xlsx
+++ b/group_input/M3_Liq_2C_WPD_InersiaCap_RevLoad.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -36,7 +35,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -59,14 +63,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -149,44 +163,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -213,14 +227,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -247,6 +279,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,166 +308,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -427,74 +453,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="13.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.21875" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameters</t>
-        </is>
-      </c>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version  </t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>GROUP2019.11.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analysis Mode </t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units  </t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(Enter EN for English Units, or SI for Standard International Units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use KIPS  </t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(For English Units, enter 1 to define KIPS as units of force, or 0 for LBS )</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GROUP2019.11.3</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Analysis Mode</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3D</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(Enter EN for English Units, or SI for Standard International Units)</t>
-        </is>
-      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Use KIPS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>(For English Units, enter 1 to define KIPS as units of force, or 0 for LBS )</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="3" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -504,23 +547,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="5.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Comb-Factors</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+    <row r="2">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Load factors</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Comb. </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   N    </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Index</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Factor  </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -530,60 +616,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Comments</t>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Model full 2 cellar: 4 titik beban rig (node 3241/3233 = cellar kiri-gambar X=45,04; 3226/3234 = cellar X=55,04) + 1 beban pile cap utuh per load case. Sumber: Rev_Reaction.xlsx (w SIDL).</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Follow template to enter loading data</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Koordinat (asal = pusat cap): Coord.Y = X_midas - 50 (3241/3233 -&gt; -5,0 m; 3226/3234 -&gt; +5,0 m); Coord.Z: 3241 &amp; 3226 = -4,75 ; 3233 &amp; 3234 = +4,75 (sama dengan input 1 cellar; gambar menunjukkan jarak +-3,7 m, mohon cek).</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ii</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Excel template will not check consistency of data</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Transformasi: FX = FZrig, FY = -FXrig, FZ = FYrig, MZ = MYrig, MY = -MXrig, MX = MZrig(=0).</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>iii</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Program may crash if loading data is not consistent</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Beban 5 (X=-0,75 m, Y=0, Z=0) = berat &amp; inersia pile cap utuh 25x12x1,2 m, bukaan 2x(3,75x3,5) m, gamma 25 -&gt; W = 8212.50 kN. PGA cap = 0.455 g (0,7 x 0,65 reduksi likuefaksi). E=kh*W; ASD: H=0,7E; LRFD: H=E; arah tegak lurus 30%. Vertikal: ASD1/2 = W; LRFD1 = 1,4W; LRFD2 = 1,2W; gempa = faktor*W + 0,5H.</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>iv</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Do not leave a blank line (except at the end) for Load-Cases and Load-Comb pages</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Format halaman mengikuti template GROUP (data mulai baris 7, baris kosong pemisah antar load case di Conc.Loads-3D).</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Leave a blank line to separate data for load cases in pages:</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Conc.Loads, Spec.Disp, Stiffness and Dist.Load</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Leave a blank line to separate data for load combinations in page Comb-Factors</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>vii</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Leave at least two blank lines to indicate end of data in pages:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Conc.Loads, Spec.Disp, Stiffness, Incremental, Dist.Load and Comb-Factors</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>viii</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Data in some pages is optional, please see template example</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ix </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Data in all pages start in Row 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rev_Reaction.xlsx (sheet w SIDL), transformasi: FX=FZrig, FY=-FXrig, FZ=FYrig, MZ=MYrig, MY=-MXrig, MX=MZrig(=0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>xi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Model full 2 cellar: Coord.Y = X_midas-50 (3241/3233 -&gt; -5 m; 3226/3234 -&gt; +5 m), Coord.Z = -4,75 (3241,3226) / +4,75 (3233,3234); beban N=5 = pile cap utuh di (-0,75;0;0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>xii</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pile cap 25x12x1,2 m, bukaan 2x(3,75x3,5) m, gamma 25 kN/m3: W utuh = 8212.50 kN. PGA cap = 0.455 g (0,7 x 0,65 reduksi likuefaksi). E=kh*W; ASD H=0,7E; LRFD H=E; tegak lurus 30%. Vertikal: ASD1/2=W; LRFD1=1,4W; LRFD2=1,2W; gempa=faktor*W+0,5H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>xiii</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>M3 (likuefaksi): hanya permanen (1) dan gempa (3,4); lateral spreading tidak ditinjau; p-multiplier/Sr diatur di model GROUP.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -594,18 +823,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="9.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="13.21875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="11.109375" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="10.21875" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="9" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="10.5546875" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="9.21875" bestFit="1" customWidth="1" min="20" max="21"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" min="22" max="23"/>
+    <col width="9.5546875" bestFit="1" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Load-Cases</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Number of load cases</t>
         </is>
@@ -614,222 +858,229 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="G3" t="inlineStr">
+    <row r="2">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>General Data</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Analysis Options</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Load Case Name</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Load Case Name    </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Load Type</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Scale Factor</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Run Analysis</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Cyclic Load</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Number Cycles</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Specify</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Incremental</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Distributed</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Soil</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Iterations</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Iterations</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Options</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Options  </t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Increments</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Displacements</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Stiffness</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Loads</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Movement</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Pile Group</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Pile</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Pile Group</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Tol. Criteria</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>Displacement</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>Rotation</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Pile</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Step Inc.</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Step Inc.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>Axial Load</t>
         </is>
@@ -841,16 +1092,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -912,7 +1182,7 @@
       <c r="S7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U7" t="n">
@@ -991,7 +1261,7 @@
       <c r="S8" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U8" t="n">
@@ -1070,7 +1340,7 @@
       <c r="S9" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U9" t="n">
@@ -1149,7 +1419,7 @@
       <c r="S10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U10" t="n">
@@ -1228,7 +1498,7 @@
       <c r="S11" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U11" t="n">
@@ -1307,7 +1577,7 @@
       <c r="S12" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" s="5" t="n">
         <v>1e-06</v>
       </c>
       <c r="U12" t="n">
@@ -1327,7 +1597,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1337,124 +1607,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:K204"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="11" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" min="10" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Conc.Loads-3D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+    <row r="2">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Concentrated Loads</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      N       </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FX        </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FY        </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        MZ        </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FZ        </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        MY        </t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        MX        </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coord. X  </t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coord. Y  </t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coord. Z  </t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Load Case</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>FX</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>FY</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>MZ</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>FZ</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. X</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. Y</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. Z</t>
-        </is>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(kN)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>(kN)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(kN-m)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>(kN)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>(kN-m)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(kN-m)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2589,8 +2872,93 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2600,135 +2968,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:V6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="7.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.77734375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.44140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="8.5546875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="9.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="7.44140625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="8.5546875" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="9.33203125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="9.44140625" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="9.109375" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="9" bestFit="1" customWidth="1" min="21" max="22"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Spec.Disp.-3D</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+    <row r="2">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Specified Displacement or Concentrated Loads</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> X TYPE </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DISP. X  </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FORCE X  </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Y TYPE </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DISP. Y  </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FORCE Y  </t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RZ TYPE </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROT. RZ  </t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MOMENT MZ </t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Z TYPE </t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DISP. Z  </t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FORCE Z  </t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RY TYPE </t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROT. RY  </t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MOMENT MY </t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX TYPE </t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROT. RX  </t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MOMENT MX </t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Coord. X </t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Coord. Y </t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Coord. Z </t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Load Case</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>X TYPE</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>DISP. X</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>FORCE X</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Y TYPE</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>DISP. Y</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>FORCE Y</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>RZ TYPE</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>ROT. RZ</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>MOMENT MZ</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>Z TYPE</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>DISP. Z</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>FORCE Z</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>RY TYPE</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
-        <is>
-          <t>ROT. RY</t>
-        </is>
-      </c>
-      <c r="P5" s="1" t="inlineStr">
-        <is>
-          <t>MOMENT MY</t>
-        </is>
-      </c>
-      <c r="Q5" s="1" t="inlineStr">
-        <is>
-          <t>RX TYPE</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="inlineStr">
-        <is>
-          <t>ROT. RX</t>
-        </is>
-      </c>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>MOMENT MX</t>
-        </is>
-      </c>
-      <c r="T5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. X</t>
-        </is>
-      </c>
-      <c r="U5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. Y</t>
-        </is>
-      </c>
-      <c r="V5" s="1" t="inlineStr">
-        <is>
-          <t>Coord. Z</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>(rad)</t>
+        </is>
+      </c>
+      <c r="J5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb)","(kips)"),IF(Parameters!$C$4="SI","(kN)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>(rad)</t>
+        </is>
+      </c>
+      <c r="P5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>(rad)</t>
+        </is>
+      </c>
+      <c r="S5" s="4">
+        <f>IF(Parameters!$C$4="EN",IF(Parameters!$C$5=0,"(lb-in)","(kips-in)"),IF(Parameters!$C$4="SI","(kN-m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="T5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="U5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="V5" s="4">
+        <f>IF(Parameters!$C$4="EN","(ft)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2738,612 +3220,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:V6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.21875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="9.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.77734375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="7.21875" bestFit="1" customWidth="1" min="7" max="9"/>
+    <col width="9.21875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="6.109375" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="8.77734375" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="7.6640625" bestFit="1" customWidth="1" min="13" max="21"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stiffness</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>NonLinear Option</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Equivalent Elastic Option</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Load Case</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Compute</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Diagonal</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Axial</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Load or</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Compute </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Diagonal </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Axial  </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load or </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Scale </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Target </t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Target </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Target </t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>Max.</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Max. </t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Number </t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Factor 1</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Factor 2</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Factor 3</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Factor 4</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Factor 5</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Factor 6</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>Factor 7</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>Factor 8</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>Factor 9</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Factor 10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Stiffness</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Stiffness</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Force</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stiffness </t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stiffness </t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Force  </t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Deflection</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Only DOF</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>DOF</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Disp.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Rotat.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Iter.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Iter. </t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(m)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>(rad)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3353,23 +3467,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:AI6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.44140625" bestFit="1" customWidth="1" min="4" max="10"/>
+    <col width="7.6640625" bestFit="1" customWidth="1" min="11" max="19"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="20" max="35"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Incremental</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="n"/>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Incremental/Pushover Analysis</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Incremental </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Number </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Constant </t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 1</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 2</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 3</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 4</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 5</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 6</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 7</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 8</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 9</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 10</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 11</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 12</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 13</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 14</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 15</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 16</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 17</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 18</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 19</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 20</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 21</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 22</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 23</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 24</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>Factor 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Analysis </t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ux/Fx </t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Uy/Fy </t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rz/Mz </t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Uz/Fz </t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ry/My </t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rx/Mx </t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DL </t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+      <c r="AF5" s="4" t="n"/>
+      <c r="AG5" s="4" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n"/>
+      <c r="AA6" s="4" t="n"/>
+      <c r="AB6" s="4" t="n"/>
+      <c r="AC6" s="4" t="n"/>
+      <c r="AD6" s="4" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+      <c r="AF6" s="4" t="n"/>
+      <c r="AG6" s="4" t="n"/>
+      <c r="AH6" s="4" t="n"/>
+      <c r="AI6" s="4" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3379,23 +3784,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="7.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12.21875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="8.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Dist.Load-3D</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+    <row r="2">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Distributed Loads</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     N      </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Direction </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pile Number </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> End Pile </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pile Incr. </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Dist. Load Y</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Factor Y   </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Dist. Load Z</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Factor Z  </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set   </t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set   </t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3405,23 +3901,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="7.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12.21875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="8.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Soil Move.-3D</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+    <row r="2">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Soil Movement</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Load Case </t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     N      </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Direction </t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pile Number </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> End Pile </t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pile Incr. </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Soil Move. Y</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Factor Y   </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Soil Move. Z</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Factor Z  </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set   </t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set   </t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3431,25 +4018,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="24" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="7.5546875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="8" max="9"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="9" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="10.5546875" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="9.21875" bestFit="1" customWidth="1" min="15" max="16"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="9.21875" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="9.5546875" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Load-Comb</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Number of load combs.</t>
         </is>
       </c>
-      <c r="J1" t="n">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="2">
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>General Data</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Analysis Options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Load Combination Name  </t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Run Analysis</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Cyclic Load</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Number Cycles</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Res. Factor</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Res. Factor</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Iterations</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Iterations</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Alternative</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Increments</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Bending</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Shear</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Pile Group</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Pile</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Pile Group</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Tol. Criteria</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Pile</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Step Inc.</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Step Inc.</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>Axial Load</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>Processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4">
+        <f>IF(Parameters!$C$4="EN","(in)",IF(Parameters!$C$4="SI","(m)","Unknown"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>